--- a/eflow-diga/build/2.0.0-draft/StructureDefinition-GEM-ERP-PR-MedicationDispense-DiGA.xlsx
+++ b/eflow-diga/build/2.0.0-draft/StructureDefinition-GEM-ERP-PR-MedicationDispense-DiGA.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3660" uniqueCount="588">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3660" uniqueCount="587">
   <si>
     <t>Property</t>
   </si>
@@ -631,7 +631,7 @@
 </t>
   </si>
   <si>
-    <t>Optional Extensions Element</t>
+    <t>Extension</t>
   </si>
   <si>
     <t>This extension is used to track medication prescription transactions between the E-Rezept-Fachdienst and the ePA. The RxPrescriptionProcessIdentifier is generated by the ePA Medication Service and consists of the PrescriptionId and the authoredOn date of the operation parameters request. It ensures consistent referencing and management of medication-related resources across different systems.</t>
@@ -677,9 +677,6 @@
   <si>
     <t xml:space="preserve">Extension {https://gematik.de/fhir/erp-diga/StructureDefinition/GEM_ERP_EX_RedeemCode}
 </t>
-  </si>
-  <si>
-    <t>Extension</t>
   </si>
   <si>
     <t>An Extension</t>
@@ -4430,7 +4427,7 @@
         <v>78</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>106</v>
+        <v>190</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>78</v>
@@ -4713,10 +4710,10 @@
         <v>211</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4799,13 +4796,13 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B22" t="s" s="2">
         <v>191</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>78</v>
@@ -4827,13 +4824,13 @@
         <v>78</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="L22" t="s" s="2">
-        <v>217</v>
-      </c>
       <c r="M22" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4916,10 +4913,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4945,16 +4942,16 @@
         <v>109</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="N23" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>78</v>
@@ -5003,7 +5000,7 @@
         <v>115</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -5035,10 +5032,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5061,16 +5058,16 @@
         <v>78</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -5108,7 +5105,7 @@
         <v>78</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AC24" s="2"/>
       <c r="AD24" t="s" s="2">
@@ -5118,7 +5115,7 @@
         <v>115</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -5133,30 +5130,30 @@
         <v>100</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AL24" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="AL24" t="s" s="2">
+      <c r="AM24" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AN24" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="AN24" t="s" s="2">
+      <c r="AO24" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>233</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="C25" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="C25" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="D25" t="s" s="2">
         <v>78</v>
@@ -5178,16 +5175,16 @@
         <v>78</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="M25" t="s" s="2">
-        <v>238</v>
-      </c>
       <c r="N25" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5198,7 +5195,7 @@
         <v>78</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>78</v>
@@ -5237,7 +5234,7 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -5252,30 +5249,30 @@
         <v>100</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AL25" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="AL25" t="s" s="2">
+      <c r="AM25" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AN25" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="AN25" t="s" s="2">
+      <c r="AO25" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>233</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="C26" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="C26" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>78</v>
@@ -5297,16 +5294,16 @@
         <v>78</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="L26" t="s" s="2">
-        <v>243</v>
-      </c>
       <c r="M26" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="N26" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5317,7 +5314,7 @@
         <v>78</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>78</v>
@@ -5356,7 +5353,7 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -5371,27 +5368,27 @@
         <v>100</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AL26" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="AL26" t="s" s="2">
+      <c r="AM26" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="AM26" t="s" s="2">
+      <c r="AN26" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="AN26" t="s" s="2">
+      <c r="AO26" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>233</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5414,16 +5411,16 @@
         <v>78</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5473,7 +5470,7 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -5485,13 +5482,13 @@
         <v>150</v>
       </c>
       <c r="AJ27" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AK27" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="AK27" t="s" s="2">
+      <c r="AL27" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="AL27" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>78</v>
@@ -5505,10 +5502,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5534,13 +5531,13 @@
         <v>167</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5548,7 +5545,7 @@
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="S28" t="s" s="2">
         <v>78</v>
@@ -5566,14 +5563,14 @@
         <v>78</v>
       </c>
       <c r="X28" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="Y28" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="Y28" t="s" s="2">
+      <c r="Z28" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="Z28" t="s" s="2">
-        <v>259</v>
-      </c>
       <c r="AA28" t="s" s="2">
         <v>78</v>
       </c>
@@ -5590,7 +5587,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>88</v>
@@ -5605,16 +5602,16 @@
         <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AL28" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="AL28" t="s" s="2">
+      <c r="AM28" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="AM28" t="s" s="2">
+      <c r="AN28" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>78</v>
@@ -5622,10 +5619,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5648,13 +5645,13 @@
         <v>78</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5684,11 +5681,11 @@
         <v>157</v>
       </c>
       <c r="Y29" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="Z29" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="Z29" t="s" s="2">
-        <v>269</v>
-      </c>
       <c r="AA29" t="s" s="2">
         <v>78</v>
       </c>
@@ -5705,7 +5702,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5720,10 +5717,10 @@
         <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AL29" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="AL29" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>78</v>
@@ -5737,10 +5734,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5763,16 +5760,16 @@
         <v>78</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5798,14 +5795,14 @@
         <v>78</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="Y30" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="Z30" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="Z30" t="s" s="2">
-        <v>278</v>
-      </c>
       <c r="AA30" t="s" s="2">
         <v>78</v>
       </c>
@@ -5822,7 +5819,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5840,24 +5837,24 @@
         <v>78</v>
       </c>
       <c r="AL30" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO30" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>280</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5880,16 +5877,16 @@
         <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5939,7 +5936,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>88</v>
@@ -5954,27 +5951,27 @@
         <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AL31" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="AL31" t="s" s="2">
+      <c r="AM31" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="AM31" t="s" s="2">
+      <c r="AN31" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="AN31" t="s" s="2">
+      <c r="AO31" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>290</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6086,10 +6083,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6203,13 +6200,13 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="C34" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="C34" t="s" s="2">
-        <v>294</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>78</v>
@@ -6231,13 +6228,13 @@
         <v>78</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6306,7 +6303,7 @@
         <v>78</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>78</v>
@@ -6320,10 +6317,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="B35" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6435,10 +6432,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="B36" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="B36" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6552,10 +6549,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="B37" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="B37" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6581,13 +6578,13 @@
         <v>130</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6595,49 +6592,49 @@
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF37" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="S37" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T37" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U37" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V37" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W37" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X37" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y37" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z37" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA37" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB37" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD37" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF37" t="s" s="2">
-        <v>309</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>88</v>
@@ -6669,10 +6666,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="B38" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="B38" t="s" s="2">
-        <v>311</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6698,10 +6695,10 @@
         <v>167</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>313</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6713,7 +6710,7 @@
         <v>78</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>78</v>
@@ -6728,29 +6725,29 @@
         <v>78</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF38" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="AA38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF38" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6782,10 +6779,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6811,13 +6808,13 @@
         <v>102</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6867,16 +6864,16 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI39" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="AG39" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH39" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI39" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>100</v>
@@ -6899,10 +6896,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6928,13 +6925,13 @@
         <v>130</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6963,28 +6960,28 @@
         <v>146</v>
       </c>
       <c r="Y40" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="Z40" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="Z40" t="s" s="2">
+      <c r="AA40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF40" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="AA40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -7016,10 +7013,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7042,16 +7039,16 @@
         <v>89</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7101,7 +7098,7 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -7119,7 +7116,7 @@
         <v>78</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>78</v>
@@ -7128,15 +7125,15 @@
         <v>78</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7248,10 +7245,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7365,10 +7362,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7394,16 +7391,16 @@
         <v>167</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="N44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>78</v>
@@ -7428,31 +7425,31 @@
         <v>78</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="Y44" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="Z44" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="Z44" t="s" s="2">
+      <c r="AA44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF44" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7470,7 +7467,7 @@
         <v>78</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>78</v>
@@ -7484,10 +7481,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7510,19 +7507,19 @@
         <v>89</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="N45" t="s" s="2">
+      <c r="O45" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>351</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>78</v>
@@ -7550,28 +7547,28 @@
         <v>146</v>
       </c>
       <c r="Y45" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="Z45" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="Z45" t="s" s="2">
+      <c r="AA45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF45" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="AA45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7589,7 +7586,7 @@
         <v>78</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>78</v>
@@ -7598,15 +7595,15 @@
         <v>78</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7632,65 +7629,65 @@
         <v>130</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="N46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T46" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="S46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T46" t="s" s="2">
+      <c r="U46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF46" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="U46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF46" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7708,24 +7705,24 @@
         <v>78</v>
       </c>
       <c r="AL46" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO46" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>365</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7751,13 +7748,13 @@
         <v>102</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7771,43 +7768,43 @@
         <v>78</v>
       </c>
       <c r="T47" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF47" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="U47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7825,24 +7822,24 @@
         <v>78</v>
       </c>
       <c r="AL47" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO47" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>373</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7865,16 +7862,16 @@
         <v>89</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7924,7 +7921,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7936,30 +7933,30 @@
         <v>150</v>
       </c>
       <c r="AJ48" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL48" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="AK48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL48" t="s" s="2">
+      <c r="AM48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO48" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>382</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7982,16 +7979,16 @@
         <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8041,7 +8038,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -8053,30 +8050,30 @@
         <v>150</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL49" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO49" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>390</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8102,13 +8099,13 @@
         <v>102</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8158,7 +8155,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -8190,10 +8187,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8216,16 +8213,16 @@
         <v>89</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8275,7 +8272,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -8287,30 +8284,30 @@
         <v>150</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AK51" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AL51" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="AL51" t="s" s="2">
+      <c r="AM51" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="AM51" t="s" s="2">
+      <c r="AN51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO51" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>404</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8422,10 +8419,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8539,10 +8536,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8568,13 +8565,13 @@
         <v>102</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8624,16 +8621,16 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI54" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="AG54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH54" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI54" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>100</v>
@@ -8656,10 +8653,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8685,13 +8682,13 @@
         <v>130</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8720,10 +8717,10 @@
         <v>146</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>78</v>
@@ -8741,7 +8738,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8773,10 +8770,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8799,16 +8796,16 @@
         <v>89</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="M56" t="s" s="2">
-        <v>238</v>
-      </c>
       <c r="N56" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8858,7 +8855,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8876,7 +8873,7 @@
         <v>78</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>78</v>
@@ -8885,15 +8882,15 @@
         <v>78</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8919,13 +8916,13 @@
         <v>102</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="M57" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="N57" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8975,7 +8972,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -9007,10 +9004,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9033,16 +9030,16 @@
         <v>78</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="M58" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="M58" t="s" s="2">
-        <v>417</v>
-      </c>
       <c r="N58" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9092,7 +9089,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -9104,13 +9101,13 @@
         <v>150</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AK58" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AL58" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>78</v>
@@ -9124,10 +9121,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9150,16 +9147,16 @@
         <v>78</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="M59" t="s" s="2">
-        <v>423</v>
-      </c>
       <c r="N59" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9209,7 +9206,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -9221,16 +9218,16 @@
         <v>150</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL59" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AM59" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>425</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>78</v>
@@ -9241,10 +9238,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9267,13 +9264,13 @@
         <v>78</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9324,7 +9321,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9339,10 +9336,10 @@
         <v>100</v>
       </c>
       <c r="AK60" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AL60" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>78</v>
@@ -9356,10 +9353,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9471,10 +9468,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9588,14 +9585,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9617,16 +9614,16 @@
         <v>109</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>437</v>
       </c>
       <c r="N63" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>78</v>
@@ -9675,7 +9672,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9707,10 +9704,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9733,19 +9730,19 @@
         <v>78</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="N64" t="s" s="2">
+      <c r="O64" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>78</v>
@@ -9773,11 +9770,11 @@
         <v>157</v>
       </c>
       <c r="Y64" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="Z64" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="Z64" t="s" s="2">
-        <v>445</v>
-      </c>
       <c r="AA64" t="s" s="2">
         <v>78</v>
       </c>
@@ -9794,7 +9791,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9812,7 +9809,7 @@
         <v>78</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>78</v>
@@ -9821,15 +9818,15 @@
         <v>78</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9852,16 +9849,16 @@
         <v>78</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="L65" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="M65" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="M65" t="s" s="2">
-        <v>450</v>
-      </c>
       <c r="N65" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9911,7 +9908,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>88</v>
@@ -9923,13 +9920,13 @@
         <v>150</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AK65" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AL65" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>78</v>
@@ -9943,10 +9940,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10058,10 +10055,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10175,10 +10172,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10204,13 +10201,13 @@
         <v>102</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10260,16 +10257,16 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI68" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="AG68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH68" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI68" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>100</v>
@@ -10292,10 +10289,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10321,13 +10318,13 @@
         <v>130</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10356,28 +10353,28 @@
         <v>146</v>
       </c>
       <c r="Y69" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="Z69" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="Z69" t="s" s="2">
+      <c r="AA69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF69" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10409,10 +10406,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10435,16 +10432,16 @@
         <v>89</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="L70" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="L70" t="s" s="2">
-        <v>459</v>
-      </c>
       <c r="M70" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="N70" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10494,7 +10491,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10512,7 +10509,7 @@
         <v>78</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>78</v>
@@ -10521,15 +10518,15 @@
         <v>78</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10555,13 +10552,13 @@
         <v>102</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="M71" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="N71" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10611,7 +10608,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10643,10 +10640,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10669,16 +10666,16 @@
         <v>78</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="L72" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="L72" t="s" s="2">
+      <c r="M72" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="M72" t="s" s="2">
-        <v>464</v>
-      </c>
       <c r="N72" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10728,7 +10725,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10740,13 +10737,13 @@
         <v>150</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>78</v>
@@ -10760,10 +10757,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10786,16 +10783,16 @@
         <v>78</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="L73" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="L73" t="s" s="2">
+      <c r="M73" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="N73" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>470</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10845,7 +10842,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10857,30 +10854,30 @@
         <v>150</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AK73" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="AL73" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="AL73" t="s" s="2">
+      <c r="AM73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN73" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="AM73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN73" t="s" s="2">
+      <c r="AO73" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="AO73" t="s" s="2">
-        <v>474</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10992,10 +10989,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11109,10 +11106,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11138,13 +11135,13 @@
         <v>102</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="N76" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11194,16 +11191,16 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI76" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="AG76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH76" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI76" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>100</v>
@@ -11226,10 +11223,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11255,13 +11252,13 @@
         <v>130</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="M77" t="s" s="2">
+      <c r="N77" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11290,10 +11287,10 @@
         <v>146</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>78</v>
@@ -11311,7 +11308,7 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -11343,10 +11340,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11369,16 +11366,16 @@
         <v>89</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="M78" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="N78" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11428,7 +11425,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -11446,7 +11443,7 @@
         <v>78</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>78</v>
@@ -11455,15 +11452,15 @@
         <v>78</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11489,13 +11486,13 @@
         <v>102</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="M79" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="N79" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11545,7 +11542,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11577,10 +11574,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11603,16 +11600,16 @@
         <v>78</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="M80" t="s" s="2">
-        <v>483</v>
-      </c>
       <c r="N80" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11641,11 +11638,11 @@
         <v>157</v>
       </c>
       <c r="Y80" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="Z80" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="Z80" t="s" s="2">
-        <v>484</v>
-      </c>
       <c r="AA80" t="s" s="2">
         <v>78</v>
       </c>
@@ -11662,7 +11659,7 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11680,24 +11677,24 @@
         <v>78</v>
       </c>
       <c r="AL80" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN80" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="AM80" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN80" t="s" s="2">
+      <c r="AO80" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="AO80" t="s" s="2">
-        <v>487</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11720,16 +11717,16 @@
         <v>78</v>
       </c>
       <c r="K81" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="L81" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="L81" t="s" s="2">
+      <c r="M81" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="M81" t="s" s="2">
+      <c r="N81" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>492</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11779,7 +11776,7 @@
         <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -11791,30 +11788,30 @@
         <v>150</v>
       </c>
       <c r="AJ81" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL81" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="AK81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL81" t="s" s="2">
+      <c r="AM81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN81" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="AM81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN81" t="s" s="2">
+      <c r="AO81" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="AO81" t="s" s="2">
-        <v>496</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11837,16 +11834,16 @@
         <v>78</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="M82" t="s" s="2">
-        <v>499</v>
-      </c>
       <c r="N82" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11896,7 +11893,7 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -11908,30 +11905,30 @@
         <v>150</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL82" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO82" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="AM82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO82" t="s" s="2">
-        <v>501</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11954,13 +11951,13 @@
         <v>89</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="L83" t="s" s="2">
         <v>503</v>
       </c>
-      <c r="L83" t="s" s="2">
+      <c r="M83" t="s" s="2">
         <v>504</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>505</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12011,7 +12008,7 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -12029,24 +12026,24 @@
         <v>78</v>
       </c>
       <c r="AL83" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN83" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="AM83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN83" t="s" s="2">
+      <c r="AO83" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="AO83" t="s" s="2">
-        <v>508</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12069,13 +12066,13 @@
         <v>78</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>510</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>511</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12126,7 +12123,7 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -12138,30 +12135,30 @@
         <v>78</v>
       </c>
       <c r="AJ84" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="AK84" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="AK84" t="s" s="2">
+      <c r="AL84" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="AL84" t="s" s="2">
-        <v>514</v>
-      </c>
       <c r="AM84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN84" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="AO84" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="AO84" t="s" s="2">
-        <v>508</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12184,16 +12181,16 @@
         <v>78</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="M85" t="s" s="2">
-        <v>517</v>
-      </c>
       <c r="N85" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12243,7 +12240,7 @@
         <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -12255,30 +12252,30 @@
         <v>150</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL85" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN85" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="AM85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN85" t="s" s="2">
+      <c r="AO85" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="AO85" t="s" s="2">
-        <v>520</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12301,16 +12298,16 @@
         <v>78</v>
       </c>
       <c r="K86" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="L86" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="L86" t="s" s="2">
+      <c r="M86" t="s" s="2">
         <v>523</v>
       </c>
-      <c r="M86" t="s" s="2">
-        <v>524</v>
-      </c>
       <c r="N86" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12360,7 +12357,7 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -12372,19 +12369,19 @@
         <v>150</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL86" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN86" t="s" s="2">
         <v>525</v>
-      </c>
-      <c r="AM86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN86" t="s" s="2">
-        <v>526</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>78</v>
@@ -12392,10 +12389,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12418,16 +12415,16 @@
         <v>78</v>
       </c>
       <c r="K87" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="L87" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="L87" t="s" s="2">
+      <c r="M87" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="M87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>531</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12477,7 +12474,7 @@
         <v>78</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -12492,27 +12489,27 @@
         <v>100</v>
       </c>
       <c r="AK87" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AL87" t="s" s="2">
         <v>532</v>
       </c>
-      <c r="AL87" t="s" s="2">
+      <c r="AM87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO87" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="AM87" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN87" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO87" t="s" s="2">
-        <v>534</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12535,16 +12532,16 @@
         <v>78</v>
       </c>
       <c r="K88" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="L88" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="L88" t="s" s="2">
+      <c r="M88" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="N88" t="s" s="2">
         <v>537</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>538</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -12594,7 +12591,7 @@
         <v>78</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -12606,13 +12603,13 @@
         <v>150</v>
       </c>
       <c r="AJ88" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL88" t="s" s="2">
         <v>539</v>
-      </c>
-      <c r="AK88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL88" t="s" s="2">
-        <v>540</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>78</v>
@@ -12626,10 +12623,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12652,16 +12649,16 @@
         <v>78</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="M89" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="M89" t="s" s="2">
+      <c r="N89" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>544</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -12711,7 +12708,7 @@
         <v>78</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -12729,13 +12726,13 @@
         <v>78</v>
       </c>
       <c r="AL89" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN89" t="s" s="2">
         <v>545</v>
-      </c>
-      <c r="AM89" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN89" t="s" s="2">
-        <v>546</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>78</v>
@@ -12743,10 +12740,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12858,10 +12855,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12975,14 +12972,14 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -13004,16 +13001,16 @@
         <v>109</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="M92" t="s" s="2">
-        <v>437</v>
       </c>
       <c r="N92" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>78</v>
@@ -13062,7 +13059,7 @@
         <v>78</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -13094,10 +13091,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13120,13 +13117,13 @@
         <v>78</v>
       </c>
       <c r="K93" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="L93" t="s" s="2">
         <v>551</v>
       </c>
-      <c r="L93" t="s" s="2">
+      <c r="M93" t="s" s="2">
         <v>552</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>553</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13177,7 +13174,7 @@
         <v>78</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>88</v>
@@ -13195,7 +13192,7 @@
         <v>78</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>78</v>
@@ -13209,10 +13206,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13235,16 +13232,16 @@
         <v>78</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>556</v>
       </c>
-      <c r="M94" t="s" s="2">
-        <v>557</v>
-      </c>
       <c r="N94" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13273,11 +13270,11 @@
         <v>157</v>
       </c>
       <c r="Y94" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="Z94" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="Z94" t="s" s="2">
-        <v>559</v>
-      </c>
       <c r="AA94" t="s" s="2">
         <v>78</v>
       </c>
@@ -13294,7 +13291,7 @@
         <v>78</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -13312,24 +13309,24 @@
         <v>78</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN94" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="AO94" t="s" s="2">
         <v>560</v>
-      </c>
-      <c r="AO94" t="s" s="2">
-        <v>561</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13352,16 +13349,16 @@
         <v>78</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>563</v>
       </c>
-      <c r="M95" t="s" s="2">
-        <v>564</v>
-      </c>
       <c r="N95" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13390,11 +13387,11 @@
         <v>157</v>
       </c>
       <c r="Y95" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="Z95" t="s" s="2">
         <v>565</v>
       </c>
-      <c r="Z95" t="s" s="2">
-        <v>566</v>
-      </c>
       <c r="AA95" t="s" s="2">
         <v>78</v>
       </c>
@@ -13411,7 +13408,7 @@
         <v>78</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -13429,24 +13426,24 @@
         <v>78</v>
       </c>
       <c r="AL95" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN95" t="s" s="2">
         <v>567</v>
       </c>
-      <c r="AM95" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN95" t="s" s="2">
-        <v>568</v>
-      </c>
       <c r="AO95" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13469,16 +13466,16 @@
         <v>78</v>
       </c>
       <c r="K96" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="L96" t="s" s="2">
         <v>570</v>
       </c>
-      <c r="L96" t="s" s="2">
+      <c r="M96" t="s" s="2">
         <v>571</v>
       </c>
-      <c r="M96" t="s" s="2">
-        <v>572</v>
-      </c>
       <c r="N96" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -13528,7 +13525,7 @@
         <v>78</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -13540,19 +13537,19 @@
         <v>150</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL96" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN96" t="s" s="2">
         <v>573</v>
-      </c>
-      <c r="AM96" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN96" t="s" s="2">
-        <v>574</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>78</v>
@@ -13560,14 +13557,14 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -13586,16 +13583,16 @@
         <v>78</v>
       </c>
       <c r="K97" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="L97" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="L97" t="s" s="2">
+      <c r="M97" t="s" s="2">
         <v>578</v>
       </c>
-      <c r="M97" t="s" s="2">
+      <c r="N97" t="s" s="2">
         <v>579</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>580</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -13645,7 +13642,7 @@
         <v>78</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -13657,13 +13654,13 @@
         <v>150</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>78</v>
@@ -13677,10 +13674,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13703,16 +13700,16 @@
         <v>78</v>
       </c>
       <c r="K98" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="L98" t="s" s="2">
         <v>583</v>
       </c>
-      <c r="L98" t="s" s="2">
+      <c r="M98" t="s" s="2">
         <v>584</v>
       </c>
-      <c r="M98" t="s" s="2">
+      <c r="N98" t="s" s="2">
         <v>585</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>586</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -13762,7 +13759,7 @@
         <v>78</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
@@ -13774,13 +13771,13 @@
         <v>150</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>78</v>
